--- a/output/2026-09-15_16_Croazia_Požeško-slavonska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-15_16_Croazia_Požeško-slavonska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,6 @@
           <t>Građevinski materijal Letinić d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Požega, Požeško-slavonska</t>
@@ -575,7 +574,6 @@
           <t>+385 34 276 032</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>BORDERLINE: attivo dal 1995. Attività prevalente vendita al dettaglio ferramenta/materiali edili/vernici/vetro (NKD 47520), non specificamente utensileria industriale o macchine utensili. Verificare offerta prodotti prima di contattare.</t>
